--- a/report/eval_step_structurer_v2.xlsx
+++ b/report/eval_step_structurer_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haeb/Workspaces/BioProtocol/report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBA88B77-1CAA-D54E-9A5A-62D6B11C0779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840771C3-089B-C643-A6AF-2823881FCD7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-34740" yWindow="-4360" windowWidth="28100" windowHeight="17380" xr2:uid="{95AC5CD3-31B3-F14C-98F9-2ABE9FE96B99}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="66">
   <si>
     <t>protocol_id</t>
   </si>
@@ -1237,11 +1237,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27EA8F0E-66AA-584E-ABB2-84CF8F8BC14B}">
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="8" max="15" width="0" hidden="1" customWidth="1"/>
+    <col min="8" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="0.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1355,364 +1356,364 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0.224</v>
       </c>
       <c r="F3">
-        <v>0.93200000000000005</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0.96499999999999997</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="H3">
-        <v>-0.08</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="I3">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M49" si="0">J3/I3</f>
-        <v>2.2222222222222223E-2</v>
+        <f>J3/I3</f>
+        <v>0.21428571428571427</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N49" si="1">L3/K3</f>
-        <v>1.5384615384615385E-2</v>
+        <f>L3/K3</f>
+        <v>7.407407407407407E-2</v>
       </c>
       <c r="O3" s="2">
-        <v>0.122</v>
+        <v>0.41789999999999999</v>
       </c>
       <c r="P3" s="2">
-        <v>0.625</v>
-      </c>
-      <c r="Q3" s="3" t="b">
-        <f t="shared" ref="Q3:Q49" si="2">(P3&lt;G3)</f>
-        <v>1</v>
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="Q3" t="b">
+        <f>(P3&lt;G3)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C4">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>0.224</v>
+        <v>0.35699999999999998</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>0.36599999999999999</v>
+        <v>0.52600000000000002</v>
       </c>
       <c r="H4">
-        <v>0.89300000000000002</v>
+        <v>0.47399999999999998</v>
       </c>
       <c r="I4">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <f t="shared" si="0"/>
-        <v>0.21428571428571427</v>
+        <f>J4/I4</f>
+        <v>3.125E-2</v>
       </c>
       <c r="N4">
-        <f t="shared" si="1"/>
-        <v>7.407407407407407E-2</v>
+        <f>L4/K4</f>
+        <v>0.16129032258064516</v>
       </c>
       <c r="O4" s="2">
-        <v>0.41789999999999999</v>
+        <v>0.71430000000000005</v>
       </c>
       <c r="P4" s="2">
-        <v>0.55600000000000005</v>
+        <v>0.76900000000000002</v>
       </c>
       <c r="Q4" t="b">
-        <f t="shared" si="2"/>
+        <f>(P4&lt;G4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C5">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E5">
-        <v>0.35699999999999998</v>
+        <v>0.623</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0.52600000000000002</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="H5">
-        <v>0.47399999999999998</v>
+        <v>0.495</v>
       </c>
       <c r="I5">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="K5">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <f t="shared" si="0"/>
-        <v>3.125E-2</v>
+        <f>J5/I5</f>
+        <v>1.9230769230769232E-2</v>
       </c>
       <c r="N5">
-        <f t="shared" si="1"/>
-        <v>0.16129032258064516</v>
+        <f>L5/K5</f>
+        <v>0.109375</v>
       </c>
       <c r="O5" s="2">
-        <v>0.71430000000000005</v>
+        <v>0.34429999999999999</v>
       </c>
       <c r="P5" s="2">
-        <v>0.76900000000000002</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="Q5" t="b">
-        <f t="shared" si="2"/>
+        <f>(P5&lt;G5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C6">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>0.623</v>
+        <v>0.57899999999999996</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>0.76800000000000002</v>
+        <v>0.73299999999999998</v>
       </c>
       <c r="H6">
-        <v>0.495</v>
+        <v>0.151</v>
       </c>
       <c r="I6">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <f t="shared" si="0"/>
-        <v>1.9230769230769232E-2</v>
+        <f>J6/I6</f>
+        <v>0</v>
       </c>
       <c r="N6">
-        <f t="shared" si="1"/>
-        <v>0.109375</v>
+        <f>L6/K6</f>
+        <v>0</v>
       </c>
       <c r="O6" s="2">
-        <v>0.34429999999999999</v>
+        <v>0.42109999999999997</v>
       </c>
       <c r="P6" s="2">
-        <v>0.93200000000000005</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="Q6" t="b">
-        <f t="shared" si="2"/>
+        <f>(P6&lt;G6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B7">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C7">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0.53800000000000003</v>
       </c>
       <c r="F7">
-        <v>0.68100000000000005</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>0.81</v>
+        <v>0.7</v>
       </c>
       <c r="H7">
-        <v>-8.7999999999999995E-2</v>
+        <v>-2.8000000000000001E-2</v>
       </c>
       <c r="I7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <f t="shared" si="0"/>
+        <f>J7/I7</f>
         <v>0</v>
       </c>
       <c r="N7">
-        <f t="shared" si="1"/>
-        <v>7.1428571428571425E-2</v>
+        <f>L7/K7</f>
+        <v>2.3255813953488372E-2</v>
       </c>
       <c r="O7" s="2">
-        <v>0.8125</v>
+        <v>0.81540000000000001</v>
       </c>
       <c r="P7" s="2">
-        <v>0.55400000000000005</v>
-      </c>
-      <c r="Q7" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="Q7" t="b">
+        <f>(P7&lt;G7)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C8">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="D8">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E8">
-        <v>0.97599999999999998</v>
+        <v>0.55400000000000005</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>0.98799999999999999</v>
+        <v>0.71299999999999997</v>
       </c>
       <c r="H8">
-        <v>0.189</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="I8">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M8">
-        <f t="shared" si="0"/>
-        <v>2.2727272727272728E-2</v>
+        <f>J8/I8</f>
+        <v>0</v>
       </c>
       <c r="N8">
-        <f t="shared" si="1"/>
-        <v>2.5974025974025976E-2</v>
+        <f>L8/K8</f>
+        <v>6.0606060606060608E-2</v>
       </c>
       <c r="O8" s="2">
-        <v>0.68289999999999995</v>
+        <v>0.6462</v>
       </c>
       <c r="P8" s="2">
-        <v>0.80600000000000005</v>
-      </c>
-      <c r="Q8" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="Q8" t="b">
+        <f>(P8&lt;G8)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B9">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C9">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E9">
-        <v>0.90900000000000003</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9">
-        <v>0.95199999999999996</v>
+        <v>0.56399999999999995</v>
       </c>
       <c r="H9">
-        <v>-0.35099999999999998</v>
+        <v>-7.6999999999999999E-2</v>
       </c>
       <c r="I9">
         <v>31</v>
@@ -1721,1232 +1722,1233 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9">
-        <f t="shared" si="0"/>
+        <f>J9/I9</f>
         <v>0</v>
       </c>
       <c r="N9">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>L9/K9</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="O9" s="2">
-        <v>0.2727</v>
+        <v>0.41070000000000001</v>
       </c>
       <c r="P9" s="2">
-        <v>0.88900000000000001</v>
-      </c>
-      <c r="Q9" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.88</v>
+      </c>
+      <c r="Q9" t="b">
+        <f>(P9&lt;G9)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="C10">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D10">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E10">
-        <v>0.57899999999999996</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0.67600000000000005</v>
       </c>
       <c r="G10">
-        <v>0.73299999999999998</v>
+        <v>0.80700000000000005</v>
       </c>
       <c r="H10">
-        <v>0.151</v>
+        <v>0.251</v>
       </c>
       <c r="I10">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <f t="shared" si="0"/>
+        <f>J10/I10</f>
         <v>0</v>
       </c>
       <c r="N10">
-        <f t="shared" si="1"/>
+        <f>L10/K10</f>
         <v>0</v>
       </c>
       <c r="O10" s="2">
-        <v>0.42109999999999997</v>
+        <v>0.6522</v>
       </c>
       <c r="P10" s="2">
-        <v>0.95199999999999996</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="Q10" t="b">
-        <f t="shared" si="2"/>
+        <f>(P10&lt;G10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11">
+        <v>19</v>
+      </c>
+      <c r="C11">
+        <v>51</v>
+      </c>
+      <c r="D11">
+        <v>19</v>
+      </c>
+      <c r="E11">
+        <v>0.373</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="H11">
+        <v>-0.126</v>
+      </c>
+      <c r="I11">
         <v>21</v>
       </c>
-      <c r="B11">
-        <v>35</v>
-      </c>
-      <c r="C11">
-        <v>65</v>
-      </c>
-      <c r="D11">
-        <v>35</v>
-      </c>
-      <c r="E11">
-        <v>0.53800000000000003</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>0.7</v>
-      </c>
-      <c r="H11">
-        <v>-2.8000000000000001E-2</v>
-      </c>
-      <c r="I11">
-        <v>42</v>
-      </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11">
-        <f t="shared" si="0"/>
+        <f>J11/I11</f>
         <v>0</v>
       </c>
       <c r="N11">
-        <f t="shared" si="1"/>
-        <v>2.3255813953488372E-2</v>
+        <f>L11/K11</f>
+        <v>0.1111111111111111</v>
       </c>
       <c r="O11" s="2">
-        <v>0.81540000000000001</v>
+        <v>0.27450000000000002</v>
       </c>
       <c r="P11" s="2">
-        <v>0.90600000000000003</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="Q11" t="b">
-        <f t="shared" si="2"/>
+        <f>(P11&lt;G11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B12">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C12">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D12">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E12">
-        <v>0.55400000000000005</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
-        <v>0.71299999999999997</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="H12">
-        <v>1.7000000000000001E-2</v>
+        <v>-6.2E-2</v>
       </c>
       <c r="I12">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>J12/I12</f>
+        <v>0.14035087719298245</v>
       </c>
       <c r="N12">
-        <f t="shared" si="1"/>
-        <v>6.0606060606060608E-2</v>
+        <f>L12/K12</f>
+        <v>0.1</v>
       </c>
       <c r="O12" s="2">
-        <v>0.6462</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="P12" s="2">
-        <v>0.75900000000000001</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="Q12" t="b">
-        <f t="shared" si="2"/>
+        <f>(P12&lt;G12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B13">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C13">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D13">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E13">
-        <v>0.39300000000000002</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13">
-        <v>0.56399999999999995</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H13">
-        <v>-7.6999999999999999E-2</v>
+        <v>0.65600000000000003</v>
       </c>
       <c r="I13">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>J13/I13</f>
+        <v>0.04</v>
       </c>
       <c r="N13">
-        <f t="shared" si="1"/>
-        <v>5.8823529411764705E-2</v>
+        <f>L13/K13</f>
+        <v>0.16326530612244897</v>
       </c>
       <c r="O13" s="2">
-        <v>0.41070000000000001</v>
+        <v>0.13950000000000001</v>
       </c>
       <c r="P13" s="2">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="b">
-        <f t="shared" si="2"/>
+        <f>(P13&lt;G13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14">
         <v>24</v>
       </c>
-      <c r="B14">
-        <v>52</v>
-      </c>
       <c r="C14">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D14">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E14">
-        <v>0.82499999999999996</v>
+        <v>0.51100000000000001</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14">
-        <v>0.90400000000000003</v>
+        <v>0.67600000000000005</v>
       </c>
       <c r="H14">
-        <v>-0.20899999999999999</v>
+        <v>0.35699999999999998</v>
       </c>
       <c r="I14">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="L14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M14">
-        <f t="shared" si="0"/>
-        <v>1.9607843137254902E-2</v>
+        <f>J14/I14</f>
+        <v>0</v>
       </c>
       <c r="N14">
-        <f t="shared" si="1"/>
-        <v>5.0632911392405063E-2</v>
+        <f>L14/K14</f>
+        <v>2.9411764705882353E-2</v>
       </c>
       <c r="O14" s="2">
-        <v>0.6825</v>
+        <v>0.21279999999999999</v>
       </c>
       <c r="P14" s="2">
-        <v>0.77600000000000002</v>
-      </c>
-      <c r="Q14" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.97899999999999998</v>
+      </c>
+      <c r="Q14" t="b">
+        <f>(P14&lt;G14)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B15">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="C15">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D15">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="F15">
-        <v>0.67600000000000005</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>0.80700000000000005</v>
+        <v>0.69699999999999995</v>
       </c>
       <c r="H15">
-        <v>0.251</v>
+        <v>-0.375</v>
       </c>
       <c r="I15">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <f t="shared" si="0"/>
+        <f>J15/I15</f>
         <v>0</v>
       </c>
       <c r="N15">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>L15/K15</f>
+        <v>2.2222222222222223E-2</v>
       </c>
       <c r="O15" s="2">
-        <v>0.6522</v>
+        <v>0.3256</v>
       </c>
       <c r="P15" s="2">
-        <v>0.83799999999999997</v>
+        <v>0.92</v>
       </c>
       <c r="Q15" t="b">
-        <f t="shared" si="2"/>
+        <f>(P15&lt;G15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B16">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C16">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D16">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="E16">
-        <v>0.92300000000000004</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16">
-        <v>0.96</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="H16">
-        <v>0.497</v>
+        <v>0.41299999999999998</v>
       </c>
       <c r="I16">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <f t="shared" si="0"/>
+        <f>J16/I16</f>
         <v>0</v>
       </c>
       <c r="N16">
-        <f t="shared" si="1"/>
-        <v>1.4084507042253521E-2</v>
+        <f>L16/K16</f>
+        <v>0</v>
       </c>
       <c r="O16" s="2">
-        <v>0.3846</v>
+        <v>0.625</v>
       </c>
       <c r="P16" s="2">
-        <v>0.94099999999999995</v>
-      </c>
-      <c r="Q16" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.98</v>
+      </c>
+      <c r="Q16" t="b">
+        <f>(P16&lt;G16)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C17">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E17">
-        <v>0.373</v>
+        <v>0.46899999999999997</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17">
-        <v>0.54300000000000004</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="H17">
-        <v>-0.126</v>
+        <v>0.253</v>
       </c>
       <c r="I17">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="L17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17">
-        <f t="shared" si="0"/>
+        <f>J17/I17</f>
         <v>0</v>
       </c>
       <c r="N17">
-        <f t="shared" si="1"/>
-        <v>0.1111111111111111</v>
+        <f>L17/K17</f>
+        <v>2.6315789473684209E-2</v>
       </c>
       <c r="O17" s="2">
-        <v>0.27450000000000002</v>
+        <v>0.34689999999999999</v>
       </c>
       <c r="P17" s="2">
-        <v>0.88200000000000001</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="Q17" t="b">
-        <f t="shared" si="2"/>
+        <f>(P17&lt;G17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B18">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="C18">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="D18">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="F18">
-        <v>0.42599999999999999</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>0.59799999999999998</v>
+        <v>0.76300000000000001</v>
       </c>
       <c r="H18">
-        <v>0.36</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I18">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <f t="shared" si="0"/>
+        <f>J18/I18</f>
         <v>0</v>
       </c>
       <c r="N18">
-        <f t="shared" si="1"/>
-        <v>3.8461538461538464E-2</v>
+        <f>L18/K18</f>
+        <v>0</v>
       </c>
       <c r="O18" s="2">
-        <v>0.58620000000000005</v>
+        <v>0.83330000000000004</v>
       </c>
       <c r="P18" s="2">
-        <v>0.56799999999999995</v>
-      </c>
-      <c r="Q18" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.94299999999999995</v>
+      </c>
+      <c r="Q18" t="b">
+        <f>(P18&lt;G18)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:17">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B19">
+        <v>43</v>
+      </c>
+      <c r="C19">
         <v>33</v>
-      </c>
-      <c r="C19">
-        <v>86</v>
       </c>
       <c r="D19">
         <v>33</v>
       </c>
       <c r="E19">
-        <v>0.38400000000000001</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0.76700000000000002</v>
       </c>
       <c r="G19">
-        <v>0.55500000000000005</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="H19">
-        <v>-6.2E-2</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="I19">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="J19">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K19">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="L19">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M19">
-        <f t="shared" si="0"/>
-        <v>0.14035087719298245</v>
+        <f>J19/I19</f>
+        <v>2.8571428571428571E-2</v>
       </c>
       <c r="N19">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
+        <f>L19/K19</f>
+        <v>3.0769230769230771E-2</v>
       </c>
       <c r="O19" s="2">
-        <v>0.36049999999999999</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="P19" s="2">
-        <v>0.84799999999999998</v>
+        <v>0.93799999999999994</v>
       </c>
       <c r="Q19" t="b">
-        <f t="shared" si="2"/>
+        <f>(P19&lt;G19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B20">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C20">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D20">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E20">
-        <v>0.95299999999999996</v>
+        <v>0.68100000000000005</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="G20">
-        <v>0.97599999999999998</v>
+        <v>0.77100000000000002</v>
       </c>
       <c r="H20">
-        <v>0.65600000000000003</v>
+        <v>-0.24399999999999999</v>
       </c>
       <c r="I20">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="J20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="L20">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M20">
-        <f t="shared" si="0"/>
-        <v>0.04</v>
+        <f>J20/I20</f>
+        <v>3.0303030303030304E-2</v>
       </c>
       <c r="N20">
-        <f t="shared" si="1"/>
-        <v>0.16326530612244897</v>
+        <f>L20/K20</f>
+        <v>4.2253521126760563E-2</v>
       </c>
       <c r="O20" s="2">
-        <v>0.13950000000000001</v>
+        <v>0.51060000000000005</v>
       </c>
       <c r="P20" s="2">
-        <v>1</v>
+        <v>0.85699999999999998</v>
       </c>
       <c r="Q20" t="b">
-        <f t="shared" si="2"/>
+        <f>(P20&lt;G20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B21">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C21">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D21">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E21">
-        <v>0.79600000000000004</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="F21">
-        <v>0.97699999999999998</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>0.878</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="H21">
-        <v>4.3999999999999997E-2</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="I21">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M21">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>J21/I21</f>
+        <v>4.3478260869565216E-2</v>
       </c>
       <c r="N21">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>L21/K21</f>
+        <v>0.15384615384615385</v>
       </c>
       <c r="O21" s="2">
-        <v>0.74070000000000003</v>
+        <v>0.73680000000000001</v>
       </c>
       <c r="P21" s="2">
-        <v>0.84199999999999997</v>
-      </c>
-      <c r="Q21" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="Q21" t="b">
+        <f>(P21&lt;G21)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B22">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C22">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="D22">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E22">
-        <v>0.96199999999999997</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="F22">
-        <v>0.89300000000000002</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>0.92600000000000005</v>
+        <v>0.65900000000000003</v>
       </c>
       <c r="H22">
-        <v>-1.7999999999999999E-2</v>
+        <v>-0.127</v>
       </c>
       <c r="I22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <f t="shared" si="0"/>
+        <f>J22/I22</f>
         <v>0</v>
       </c>
       <c r="N22">
-        <f t="shared" si="1"/>
-        <v>2.5000000000000001E-2</v>
+        <f>L22/K22</f>
+        <v>0.1388888888888889</v>
       </c>
       <c r="O22" s="2">
-        <v>0.23080000000000001</v>
+        <v>0.2787</v>
       </c>
       <c r="P22" s="2">
-        <v>0.66700000000000004</v>
-      </c>
-      <c r="Q22" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="Q22" t="b">
+        <f>(P22&lt;G22)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B23">
+        <v>28</v>
+      </c>
+      <c r="C23">
+        <v>68</v>
+      </c>
+      <c r="D23">
+        <v>28</v>
+      </c>
+      <c r="E23">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="H23">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="I23">
         <v>50</v>
       </c>
-      <c r="C23">
-        <v>35</v>
-      </c>
-      <c r="D23">
-        <v>35</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23">
-        <v>0.7</v>
-      </c>
-      <c r="G23">
-        <v>0.82399999999999995</v>
-      </c>
-      <c r="H23">
-        <v>-2E-3</v>
-      </c>
-      <c r="I23">
-        <v>15</v>
-      </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="L23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <f t="shared" si="0"/>
+        <f>J23/I23</f>
         <v>0</v>
       </c>
       <c r="N23">
-        <f t="shared" si="1"/>
-        <v>5.1724137931034482E-2</v>
+        <f>L23/K23</f>
+        <v>0.14285714285714285</v>
       </c>
       <c r="O23" s="2">
-        <v>0.48570000000000002</v>
+        <v>0.17649999999999999</v>
       </c>
       <c r="P23" s="2">
-        <v>0.61099999999999999</v>
-      </c>
-      <c r="Q23" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="Q23" t="b">
+        <f>(P23&lt;G23)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B24">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C24">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D24">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E24">
-        <v>0.51100000000000001</v>
+        <v>0.35299999999999998</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24">
-        <v>0.67600000000000005</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="H24">
-        <v>0.35699999999999998</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="I24">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K24">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M24">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>J24/I24</f>
+        <v>0.125</v>
       </c>
       <c r="N24">
-        <f t="shared" si="1"/>
-        <v>2.9411764705882353E-2</v>
+        <f>L24/K24</f>
+        <v>0.14814814814814814</v>
       </c>
       <c r="O24" s="2">
-        <v>0.21279999999999999</v>
+        <v>0.35289999999999999</v>
       </c>
       <c r="P24" s="2">
-        <v>0.97899999999999998</v>
+        <v>0.75</v>
       </c>
       <c r="Q24" t="b">
-        <f t="shared" si="2"/>
+        <f>(P24&lt;G24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B25">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C25">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D25">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E25">
-        <v>0.53500000000000003</v>
+        <v>0.76900000000000002</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25">
-        <v>0.69699999999999995</v>
+        <v>0.87</v>
       </c>
       <c r="H25">
-        <v>-0.375</v>
+        <v>-0.31900000000000001</v>
       </c>
       <c r="I25">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="L25">
         <v>1</v>
       </c>
       <c r="M25">
-        <f t="shared" si="0"/>
+        <f>J25/I25</f>
         <v>0</v>
       </c>
       <c r="N25">
-        <f t="shared" si="1"/>
-        <v>2.2222222222222223E-2</v>
+        <f>L25/K25</f>
+        <v>1.8867924528301886E-2</v>
       </c>
       <c r="O25" s="2">
-        <v>0.3256</v>
+        <v>0.82050000000000001</v>
       </c>
       <c r="P25" s="2">
-        <v>0.92</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="Q25" t="b">
-        <f t="shared" si="2"/>
+        <f>(P25&lt;G25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B26">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C26">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D26">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E26">
-        <v>0.88900000000000001</v>
+        <v>0.65200000000000002</v>
       </c>
       <c r="F26">
-        <v>0.82099999999999995</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>0.85299999999999998</v>
+        <v>0.78900000000000003</v>
       </c>
       <c r="H26">
-        <v>0.248</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="I26">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M26">
-        <f t="shared" si="0"/>
-        <v>2.3809523809523808E-2</v>
+        <f>J26/I26</f>
+        <v>0</v>
       </c>
       <c r="N26">
-        <f t="shared" si="1"/>
-        <v>2.1276595744680851E-2</v>
+        <f>L26/K26</f>
+        <v>5.1724137931034482E-2</v>
       </c>
       <c r="O26" s="2">
-        <v>0.1389</v>
+        <v>0.3478</v>
       </c>
       <c r="P26" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="Q26" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="Q26" t="b">
+        <f>(P26&lt;G26)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B27">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="C27">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D27">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E27">
-        <v>0.73699999999999999</v>
+        <v>0.55900000000000005</v>
       </c>
       <c r="F27">
-        <v>0.97699999999999998</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>0.84</v>
+        <v>0.71699999999999997</v>
       </c>
       <c r="H27">
-        <v>-6.0000000000000001E-3</v>
+        <v>-0.39300000000000002</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
+        <f>J27/I27</f>
         <v>0</v>
       </c>
       <c r="N27">
-        <f t="shared" si="1"/>
+        <f>L27/K27</f>
         <v>0</v>
       </c>
       <c r="O27" s="2">
-        <v>0.29820000000000002</v>
+        <v>0.23530000000000001</v>
       </c>
       <c r="P27" s="2">
-        <v>0.73499999999999999</v>
-      </c>
-      <c r="Q27" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.745</v>
+      </c>
+      <c r="Q27" t="b">
+        <f>(P27&lt;G27)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B28">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C28">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D28">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E28">
-        <v>0.44600000000000001</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28">
-        <v>0.61699999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="H28">
-        <v>0.41299999999999998</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="I28">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28">
-        <f t="shared" si="0"/>
+        <f>J28/I28</f>
         <v>0</v>
       </c>
       <c r="N28">
-        <f t="shared" si="1"/>
+        <f>L28/K28</f>
         <v>0</v>
       </c>
       <c r="O28" s="2">
-        <v>0.625</v>
+        <v>0.375</v>
       </c>
       <c r="P28" s="2">
-        <v>0.98</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="Q28" t="b">
-        <f t="shared" si="2"/>
+        <f>(P28&lt;G28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B29">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C29">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D29">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E29">
-        <v>0.46899999999999997</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29">
-        <v>0.63900000000000001</v>
+        <v>0.64400000000000002</v>
       </c>
       <c r="H29">
-        <v>0.253</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="I29">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <f t="shared" si="0"/>
+        <f>J29/I29</f>
         <v>0</v>
       </c>
       <c r="N29">
-        <f t="shared" si="1"/>
-        <v>2.6315789473684209E-2</v>
+        <f>L29/K29</f>
+        <v>0</v>
       </c>
       <c r="O29" s="2">
-        <v>0.34689999999999999</v>
+        <v>0.375</v>
       </c>
       <c r="P29" s="2">
-        <v>0.95499999999999996</v>
+        <v>0.92700000000000005</v>
       </c>
       <c r="Q29" t="b">
-        <f t="shared" si="2"/>
+        <f>(P29&lt;G29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B30">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C30">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D30">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E30">
-        <v>0.61699999999999999</v>
+        <v>0.65700000000000003</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30">
-        <v>0.76300000000000001</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="H30">
-        <v>7.0000000000000007E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="I30">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>J30/I30</f>
+        <v>2.2988505747126436E-2</v>
       </c>
       <c r="N30">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>L30/K30</f>
+        <v>1.9230769230769232E-2</v>
       </c>
       <c r="O30" s="2">
-        <v>0.83330000000000004</v>
+        <v>0.44290000000000002</v>
       </c>
       <c r="P30" s="2">
-        <v>0.94299999999999995</v>
+        <v>0.93</v>
       </c>
       <c r="Q30" t="b">
-        <f t="shared" si="2"/>
+        <f>(P30&lt;G30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:17">
       <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31">
+        <v>44</v>
+      </c>
+      <c r="C31">
         <v>41</v>
       </c>
-      <c r="B31">
-        <v>43</v>
-      </c>
-      <c r="C31">
-        <v>33</v>
-      </c>
       <c r="D31">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31">
-        <v>0.76700000000000002</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="G31">
-        <v>0.86799999999999999</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="H31">
-        <v>0.23899999999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="I31">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2955,921 +2957,920 @@
         <v>65</v>
       </c>
       <c r="L31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M31">
-        <f t="shared" si="0"/>
-        <v>2.8571428571428571E-2</v>
+        <f>J31/I31</f>
+        <v>2.2222222222222223E-2</v>
       </c>
       <c r="N31">
-        <f t="shared" si="1"/>
-        <v>3.0769230769230771E-2</v>
+        <f>L31/K31</f>
+        <v>1.5384615384615385E-2</v>
       </c>
       <c r="O31" s="2">
-        <v>0.30299999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="P31" s="2">
-        <v>0.93799999999999994</v>
-      </c>
-      <c r="Q31" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.625</v>
+      </c>
+      <c r="Q31" s="3" t="b">
+        <f>(P31&lt;G31)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="B32">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C32">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D32">
         <v>32</v>
       </c>
       <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
         <v>0.68100000000000005</v>
       </c>
-      <c r="F32">
-        <v>0.88900000000000001</v>
-      </c>
       <c r="G32">
-        <v>0.77100000000000002</v>
+        <v>0.81</v>
       </c>
       <c r="H32">
-        <v>-0.24399999999999999</v>
+        <v>-8.7999999999999995E-2</v>
       </c>
       <c r="I32">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="L32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M32">
-        <f t="shared" si="0"/>
-        <v>3.0303030303030304E-2</v>
+        <f>J32/I32</f>
+        <v>0</v>
       </c>
       <c r="N32">
-        <f t="shared" si="1"/>
-        <v>4.2253521126760563E-2</v>
+        <f>L32/K32</f>
+        <v>7.1428571428571425E-2</v>
       </c>
       <c r="O32" s="2">
-        <v>0.51060000000000005</v>
+        <v>0.8125</v>
       </c>
       <c r="P32" s="2">
-        <v>0.85699999999999998</v>
-      </c>
-      <c r="Q32" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="Q32" s="3" t="b">
+        <f>(P32&lt;G32)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:17">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="B33">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C33">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D33">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E33">
-        <v>0.40400000000000003</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33">
-        <v>0.57499999999999996</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="H33">
-        <v>0.22600000000000001</v>
+        <v>0.189</v>
       </c>
       <c r="I33">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="K33">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="L33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M33">
-        <f t="shared" si="0"/>
-        <v>4.3478260869565216E-2</v>
+        <f>J33/I33</f>
+        <v>2.2727272727272728E-2</v>
       </c>
       <c r="N33">
-        <f t="shared" si="1"/>
-        <v>0.15384615384615385</v>
+        <f>L33/K33</f>
+        <v>2.5974025974025976E-2</v>
       </c>
       <c r="O33" s="2">
-        <v>0.73680000000000001</v>
+        <v>0.68289999999999995</v>
       </c>
       <c r="P33" s="2">
-        <v>0.95499999999999996</v>
-      </c>
-      <c r="Q33" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.80600000000000005</v>
+      </c>
+      <c r="Q33" s="3" t="b">
+        <f>(P33&lt;G33)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:17">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="B34">
         <v>30</v>
       </c>
       <c r="C34">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="D34">
         <v>30</v>
       </c>
       <c r="E34">
-        <v>0.49199999999999999</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34">
-        <v>0.65900000000000003</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="H34">
-        <v>-0.127</v>
+        <v>-0.35099999999999998</v>
       </c>
       <c r="I34">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="L34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M34">
-        <f t="shared" si="0"/>
+        <f>J34/I34</f>
         <v>0</v>
       </c>
       <c r="N34">
-        <f t="shared" si="1"/>
-        <v>0.1388888888888889</v>
+        <f>L34/K34</f>
+        <v>0</v>
       </c>
       <c r="O34" s="2">
-        <v>0.2787</v>
+        <v>0.2727</v>
       </c>
       <c r="P34" s="2">
-        <v>0.92900000000000005</v>
-      </c>
-      <c r="Q34" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="Q34" s="3" t="b">
+        <f>(P34&lt;G34)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:17">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="B35">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C35">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D35">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="E35">
-        <v>0.41199999999999998</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35">
-        <v>0.58299999999999996</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="H35">
-        <v>0.34899999999999998</v>
+        <v>-0.20899999999999999</v>
       </c>
       <c r="I35">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="L35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M35">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>J35/I35</f>
+        <v>1.9607843137254902E-2</v>
       </c>
       <c r="N35">
-        <f t="shared" si="1"/>
-        <v>0.14285714285714285</v>
+        <f>L35/K35</f>
+        <v>5.0632911392405063E-2</v>
       </c>
       <c r="O35" s="2">
-        <v>0.17649999999999999</v>
+        <v>0.6825</v>
       </c>
       <c r="P35" s="2">
-        <v>0.66700000000000004</v>
-      </c>
-      <c r="Q35" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.77600000000000002</v>
+      </c>
+      <c r="Q35" s="3" t="b">
+        <f>(P35&lt;G35)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:17">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B36">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C36">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="D36">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0.92300000000000004</v>
       </c>
       <c r="F36">
-        <v>0.64700000000000002</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>0.78600000000000003</v>
+        <v>0.96</v>
       </c>
       <c r="H36">
-        <v>-0.218</v>
+        <v>0.497</v>
       </c>
       <c r="I36">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="L36">
         <v>1</v>
       </c>
       <c r="M36">
-        <f t="shared" si="0"/>
+        <f>J36/I36</f>
         <v>0</v>
       </c>
       <c r="N36">
-        <f t="shared" si="1"/>
-        <v>1.7241379310344827E-2</v>
+        <f>L36/K36</f>
+        <v>1.4084507042253521E-2</v>
       </c>
       <c r="O36" s="2">
-        <v>9.0899999999999995E-2</v>
+        <v>0.3846</v>
       </c>
       <c r="P36" s="2">
-        <v>0.60299999999999998</v>
+        <v>0.94099999999999995</v>
       </c>
       <c r="Q36" s="3" t="b">
-        <f t="shared" si="2"/>
+        <f>(P36&lt;G36)</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:17">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="B37">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="C37">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="D37">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E37">
-        <v>0.35299999999999998</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>0.42599999999999999</v>
       </c>
       <c r="G37">
-        <v>0.52200000000000002</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="H37">
-        <v>4.9000000000000002E-2</v>
+        <v>0.36</v>
       </c>
       <c r="I37">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="L37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M37">
-        <f t="shared" si="0"/>
-        <v>0.125</v>
+        <f>J37/I37</f>
+        <v>0</v>
       </c>
       <c r="N37">
-        <f t="shared" si="1"/>
-        <v>0.14814814814814814</v>
+        <f>L37/K37</f>
+        <v>3.8461538461538464E-2</v>
       </c>
       <c r="O37" s="2">
-        <v>0.35289999999999999</v>
+        <v>0.58620000000000005</v>
       </c>
       <c r="P37" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="Q37" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.56799999999999995</v>
+      </c>
+      <c r="Q37" s="3" t="b">
+        <f>(P37&lt;G37)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:17">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B38">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="C38">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D38">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0.79600000000000004</v>
       </c>
       <c r="F38">
-        <v>0.52700000000000002</v>
+        <v>0.97699999999999998</v>
       </c>
       <c r="G38">
-        <v>0.69</v>
+        <v>0.878</v>
       </c>
       <c r="H38">
-        <v>0.45900000000000002</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="I38">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="L38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <f t="shared" si="0"/>
-        <v>3.5714285714285712E-2</v>
+        <f>J38/I38</f>
+        <v>0</v>
       </c>
       <c r="N38">
-        <f t="shared" si="1"/>
-        <v>2.0833333333333332E-2</v>
+        <f>L38/K38</f>
+        <v>0</v>
       </c>
       <c r="O38" s="2">
-        <v>0.56410000000000005</v>
+        <v>0.74070000000000003</v>
       </c>
       <c r="P38" s="2">
-        <v>0.505</v>
+        <v>0.84199999999999997</v>
       </c>
       <c r="Q38" s="3" t="b">
-        <f t="shared" si="2"/>
+        <f>(P38&lt;G38)</f>
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B39">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C39">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D39">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="F39">
-        <v>0.9</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="G39">
-        <v>0.94699999999999995</v>
+        <v>0.92600000000000005</v>
       </c>
       <c r="H39">
-        <v>0.29399999999999998</v>
+        <v>-1.7999999999999999E-2</v>
       </c>
       <c r="I39">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L39">
         <v>1</v>
       </c>
       <c r="M39">
-        <f t="shared" si="0"/>
+        <f>J39/I39</f>
         <v>0</v>
       </c>
       <c r="N39">
-        <f t="shared" si="1"/>
-        <v>2.7777777777777776E-2</v>
+        <f>L39/K39</f>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="O39" s="2">
-        <v>0.37040000000000001</v>
+        <v>0.23080000000000001</v>
       </c>
       <c r="P39" s="2">
-        <v>0.75</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="Q39" s="3" t="b">
-        <f t="shared" si="2"/>
+        <f>(P39&lt;G39)</f>
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:17">
       <c r="A40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40">
         <v>50</v>
       </c>
-      <c r="B40">
-        <v>30</v>
-      </c>
       <c r="C40">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D40">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E40">
-        <v>0.76900000000000002</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="G40">
-        <v>0.87</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="H40">
-        <v>-0.31900000000000001</v>
+        <v>-2E-3</v>
       </c>
       <c r="I40">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
       <c r="K40">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M40">
-        <f t="shared" si="0"/>
+        <f>J40/I40</f>
         <v>0</v>
       </c>
       <c r="N40">
-        <f t="shared" si="1"/>
-        <v>1.8867924528301886E-2</v>
+        <f>L40/K40</f>
+        <v>5.1724137931034482E-2</v>
       </c>
       <c r="O40" s="2">
-        <v>0.82050000000000001</v>
+        <v>0.48570000000000002</v>
       </c>
       <c r="P40" s="2">
-        <v>0.90900000000000003</v>
-      </c>
-      <c r="Q40" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="Q40" s="3" t="b">
+        <f>(P40&lt;G40)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B41">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C41">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D41">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E41">
-        <v>0.96199999999999997</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="F41">
-        <v>0.89300000000000002</v>
+        <v>0.82099999999999995</v>
       </c>
       <c r="G41">
-        <v>0.92600000000000005</v>
+        <v>0.85299999999999998</v>
       </c>
       <c r="H41">
-        <v>0.35099999999999998</v>
+        <v>0.248</v>
       </c>
       <c r="I41">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="L41">
         <v>1</v>
       </c>
       <c r="M41">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>J41/I41</f>
+        <v>2.3809523809523808E-2</v>
       </c>
       <c r="N41">
-        <f t="shared" si="1"/>
-        <v>1.5625E-2</v>
+        <f>L41/K41</f>
+        <v>2.1276595744680851E-2</v>
       </c>
       <c r="O41" s="2">
-        <v>0.15379999999999999</v>
+        <v>0.1389</v>
       </c>
       <c r="P41" s="2">
-        <v>0.88200000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="Q41" s="3" t="b">
-        <f t="shared" si="2"/>
+        <f>(P41&lt;G41)</f>
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B42">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C42">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D42">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E42">
-        <v>0.65200000000000002</v>
+        <v>0.73699999999999999</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>0.97699999999999998</v>
       </c>
       <c r="G42">
-        <v>0.78900000000000003</v>
+        <v>0.84</v>
       </c>
       <c r="H42">
-        <v>0.26500000000000001</v>
+        <v>-6.0000000000000001E-3</v>
       </c>
       <c r="I42">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J42">
         <v>0</v>
       </c>
       <c r="K42">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N42">
-        <f t="shared" si="1"/>
-        <v>5.1724137931034482E-2</v>
+        <f>L42/K42</f>
+        <v>0</v>
       </c>
       <c r="O42" s="2">
-        <v>0.3478</v>
+        <v>0.29820000000000002</v>
       </c>
       <c r="P42" s="2">
-        <v>0.92900000000000005</v>
-      </c>
-      <c r="Q42" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="Q42" s="3" t="b">
+        <f>(P42&lt;G42)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B43">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="C43">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D43">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E43">
-        <v>0.55900000000000005</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>0.64700000000000002</v>
       </c>
       <c r="G43">
-        <v>0.71699999999999997</v>
+        <v>0.78600000000000003</v>
       </c>
       <c r="H43">
-        <v>-0.39300000000000002</v>
+        <v>-0.218</v>
       </c>
       <c r="I43">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43">
-        <f t="shared" si="0"/>
+        <f>J43/I43</f>
         <v>0</v>
       </c>
       <c r="N43">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>L43/K43</f>
+        <v>1.7241379310344827E-2</v>
       </c>
       <c r="O43" s="2">
-        <v>0.23530000000000001</v>
+        <v>9.0899999999999995E-2</v>
       </c>
       <c r="P43" s="2">
-        <v>0.745</v>
-      </c>
-      <c r="Q43" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="Q43" s="3" t="b">
+        <f>(P43&lt;G43)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B44">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="C44">
+        <v>39</v>
+      </c>
+      <c r="D44">
+        <v>39</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>0.52700000000000002</v>
+      </c>
+      <c r="G44">
+        <v>0.69</v>
+      </c>
+      <c r="H44">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="I44">
+        <v>28</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44">
         <v>48</v>
       </c>
-      <c r="D44">
-        <v>32</v>
-      </c>
-      <c r="E44">
-        <v>0.66700000000000004</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44">
-        <v>0.8</v>
-      </c>
-      <c r="H44">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="I44">
-        <v>36</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>37</v>
-      </c>
       <c r="L44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>J44/I44</f>
+        <v>3.5714285714285712E-2</v>
       </c>
       <c r="N44">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>L44/K44</f>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="O44" s="2">
-        <v>0.375</v>
+        <v>0.56410000000000005</v>
       </c>
       <c r="P44" s="2">
-        <v>0.98399999999999999</v>
-      </c>
-      <c r="Q44" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.505</v>
+      </c>
+      <c r="Q44" s="3" t="b">
+        <f>(P44&lt;G44)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B45">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C45">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D45">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E45">
-        <v>0.90500000000000003</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>0.80900000000000005</v>
+        <v>0.9</v>
       </c>
       <c r="G45">
-        <v>0.85399999999999998</v>
+        <v>0.94699999999999995</v>
       </c>
       <c r="H45">
-        <v>0.121</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
       <c r="K45">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="L45">
         <v>1</v>
       </c>
       <c r="M45">
-        <f t="shared" si="0"/>
+        <f>J45/I45</f>
         <v>0</v>
       </c>
       <c r="N45">
-        <f t="shared" si="1"/>
-        <v>1.6129032258064516E-2</v>
+        <f>L45/K45</f>
+        <v>2.7777777777777776E-2</v>
       </c>
       <c r="O45" s="2">
-        <v>0.23810000000000001</v>
+        <v>0.37040000000000001</v>
       </c>
       <c r="P45" s="2">
-        <v>0.61799999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q45" s="3" t="b">
-        <f t="shared" si="2"/>
+        <f>(P45&lt;G45)</f>
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:17">
       <c r="A46" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46">
         <v>56</v>
       </c>
-      <c r="B46">
-        <v>19</v>
-      </c>
       <c r="C46">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D46">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="E46">
-        <v>0.47499999999999998</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="G46">
-        <v>0.64400000000000002</v>
+        <v>0.92600000000000005</v>
       </c>
       <c r="H46">
-        <v>0.17699999999999999</v>
+        <v>0.35099999999999998</v>
       </c>
       <c r="I46">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="J46">
         <v>0</v>
       </c>
       <c r="K46">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46">
-        <f t="shared" si="0"/>
+        <f>J46/I46</f>
         <v>0</v>
       </c>
       <c r="N46">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>L46/K46</f>
+        <v>1.5625E-2</v>
       </c>
       <c r="O46" s="2">
-        <v>0.375</v>
+        <v>0.15379999999999999</v>
       </c>
       <c r="P46" s="2">
-        <v>0.92700000000000005</v>
-      </c>
-      <c r="Q46" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.88200000000000001</v>
+      </c>
+      <c r="Q46" s="3" t="b">
+        <f>(P46&lt;G46)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B47">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C47">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="D47">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E47">
-        <v>0.65700000000000003</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>0.80900000000000005</v>
       </c>
       <c r="G47">
-        <v>0.79300000000000004</v>
+        <v>0.85399999999999998</v>
       </c>
       <c r="H47">
-        <v>5.8000000000000003E-2</v>
+        <v>0.121</v>
       </c>
       <c r="I47">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K47">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L47">
         <v>1</v>
       </c>
       <c r="M47">
-        <f t="shared" si="0"/>
-        <v>2.2988505747126436E-2</v>
+        <f>J47/I47</f>
+        <v>0</v>
       </c>
       <c r="N47">
-        <f t="shared" si="1"/>
-        <v>1.9230769230769232E-2</v>
+        <f>L47/K47</f>
+        <v>1.6129032258064516E-2</v>
       </c>
       <c r="O47" s="2">
-        <v>0.44290000000000002</v>
+        <v>0.23810000000000001</v>
       </c>
       <c r="P47" s="2">
-        <v>0.93</v>
-      </c>
-      <c r="Q47" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="Q47" s="3" t="b">
+        <f>(P47&lt;G47)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:17">
@@ -3881,59 +3882,59 @@
         <v>36.304347826086953</v>
       </c>
       <c r="C48">
-        <f t="shared" ref="C48:L48" si="3">AVERAGE(C2:C47)</f>
+        <f>AVERAGE(C2:C47)</f>
         <v>49</v>
       </c>
       <c r="D48">
-        <f t="shared" si="3"/>
+        <f>AVERAGE(D2:D47)</f>
         <v>32.152173913043477</v>
       </c>
       <c r="E48">
         <f>AVERAGE(E2:E47)</f>
-        <v>0.69806521739130445</v>
+        <v>0.69806521739130434</v>
       </c>
       <c r="F48">
-        <f t="shared" si="3"/>
-        <v>0.92423913043478267</v>
+        <f>AVERAGE(F2:F47)</f>
+        <v>0.92423913043478245</v>
       </c>
       <c r="G48">
-        <f t="shared" si="3"/>
-        <v>0.75315217391304323</v>
+        <f>AVERAGE(G2:G47)</f>
+        <v>0.75315217391304357</v>
       </c>
       <c r="H48">
-        <f t="shared" si="3"/>
+        <f>AVERAGE(H2:H47)</f>
         <v>0.12076086956521738</v>
       </c>
       <c r="I48">
-        <f t="shared" si="3"/>
+        <f>AVERAGE(I2:I47)</f>
         <v>34.456521739130437</v>
       </c>
       <c r="J48">
-        <f t="shared" si="3"/>
+        <f>AVERAGE(J2:J47)</f>
         <v>0.69565217391304346</v>
       </c>
       <c r="K48">
-        <f t="shared" si="3"/>
+        <f>AVERAGE(K2:K47)</f>
         <v>50.043478260869563</v>
       </c>
       <c r="L48">
-        <f t="shared" si="3"/>
+        <f>AVERAGE(L2:L47)</f>
         <v>2.1304347826086958</v>
       </c>
       <c r="M48">
-        <f t="shared" ref="M48" si="4">AVERAGE(M2:M47)</f>
+        <f>AVERAGE(M2:M47)</f>
         <v>1.8474842698134916E-2</v>
       </c>
       <c r="N48">
-        <f t="shared" ref="N48:O48" si="5">AVERAGE(N2:N47)</f>
-        <v>4.7217052428272427E-2</v>
+        <f>AVERAGE(N2:N47)</f>
+        <v>4.7217052428272434E-2</v>
       </c>
       <c r="O48">
-        <f t="shared" si="5"/>
-        <v>0.43152608695652178</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+        <f>AVERAGE(O2:O47)</f>
+        <v>0.43152608695652184</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17">
       <c r="A49" t="s">
         <v>59</v>
       </c>
@@ -3942,59 +3943,59 @@
         <v>74</v>
       </c>
       <c r="C49">
-        <f t="shared" ref="C49:O49" si="6">MAX(C2:C47)</f>
+        <f>MAX(C2:C47)</f>
         <v>86</v>
       </c>
       <c r="D49">
-        <f t="shared" si="6"/>
+        <f>MAX(D2:D47)</f>
         <v>52</v>
       </c>
       <c r="E49">
-        <f t="shared" si="6"/>
+        <f>MAX(E2:E47)</f>
         <v>1</v>
       </c>
       <c r="F49">
-        <f t="shared" si="6"/>
+        <f>MAX(F2:F47)</f>
         <v>1</v>
       </c>
       <c r="G49">
-        <f t="shared" si="6"/>
+        <f>MAX(G2:G47)</f>
         <v>0.98799999999999999</v>
       </c>
       <c r="H49">
-        <f t="shared" si="6"/>
+        <f>MAX(H2:H47)</f>
         <v>0.89300000000000002</v>
       </c>
       <c r="I49">
-        <f t="shared" si="6"/>
+        <f>MAX(I2:I47)</f>
         <v>102</v>
       </c>
       <c r="J49">
-        <f t="shared" si="6"/>
+        <f>MAX(J2:J47)</f>
         <v>8</v>
       </c>
       <c r="K49">
-        <f t="shared" si="6"/>
+        <f>MAX(K2:K47)</f>
         <v>92</v>
       </c>
       <c r="L49">
-        <f t="shared" si="6"/>
+        <f>MAX(L2:L47)</f>
         <v>8</v>
       </c>
       <c r="M49">
-        <f t="shared" si="6"/>
+        <f>MAX(M2:M47)</f>
         <v>0.21428571428571427</v>
       </c>
       <c r="N49">
-        <f t="shared" si="6"/>
+        <f>MAX(N2:N47)</f>
         <v>0.16326530612244897</v>
       </c>
       <c r="O49">
-        <f t="shared" si="6"/>
+        <f>MAX(O2:O47)</f>
         <v>0.83330000000000004</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:17">
       <c r="A50" t="s">
         <v>60</v>
       </c>
@@ -4003,59 +4004,279 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <f t="shared" ref="C50:O50" si="7">MIN(C2:C47)</f>
+        <f>MIN(C2:C47)</f>
         <v>26</v>
       </c>
       <c r="D50">
-        <f t="shared" si="7"/>
+        <f>MIN(D2:D47)</f>
         <v>15</v>
       </c>
       <c r="E50">
-        <f t="shared" si="7"/>
+        <f>MIN(E2:E47)</f>
         <v>0.224</v>
       </c>
       <c r="F50">
-        <f t="shared" si="7"/>
+        <f>MIN(F2:F47)</f>
         <v>0.42599999999999999</v>
       </c>
       <c r="G50">
-        <f t="shared" si="7"/>
+        <f>MIN(G2:G47)</f>
         <v>0.36599999999999999</v>
       </c>
       <c r="H50">
-        <f t="shared" si="7"/>
+        <f>MIN(H2:H47)</f>
         <v>-0.39300000000000002</v>
       </c>
       <c r="I50">
-        <f t="shared" si="7"/>
+        <f>MIN(I2:I47)</f>
         <v>0</v>
       </c>
       <c r="J50">
-        <f t="shared" si="7"/>
+        <f>MIN(J2:J47)</f>
         <v>0</v>
       </c>
       <c r="K50">
-        <f t="shared" si="7"/>
+        <f>MIN(K2:K47)</f>
         <v>18</v>
       </c>
       <c r="L50">
-        <f t="shared" si="7"/>
+        <f>MIN(L2:L47)</f>
         <v>0</v>
       </c>
       <c r="M50">
-        <f t="shared" si="7"/>
+        <f>MIN(M2:M47)</f>
         <v>0</v>
       </c>
       <c r="N50">
-        <f t="shared" si="7"/>
+        <f>MIN(N2:N47)</f>
         <v>0</v>
       </c>
       <c r="O50">
-        <f t="shared" si="7"/>
+        <f>MIN(O2:O47)</f>
         <v>9.0899999999999995E-2</v>
       </c>
     </row>
+    <row r="51" spans="1:17">
+      <c r="B51">
+        <f>AVERAGE(B31:B47)</f>
+        <v>46.529411764705884</v>
+      </c>
+      <c r="C51">
+        <f t="shared" ref="C51:Q51" si="0">AVERAGE(C31:C47)</f>
+        <v>40.705882352941174</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="0"/>
+        <v>37.411764705882355</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="0"/>
+        <v>0.9343529411764705</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="0"/>
+        <v>0.83429411764705885</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="0"/>
+        <v>0.86476470588235277</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="0"/>
+        <v>9.3588235294117653E-2</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="0"/>
+        <v>32.941176470588232</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="0"/>
+        <v>0.35294117647058826</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="0"/>
+        <v>58.588235294117645</v>
+      </c>
+      <c r="L51">
+        <f t="shared" si="0"/>
+        <v>1.411764705882353</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="0"/>
+        <v>7.2988910359152569E-3</v>
+      </c>
+      <c r="N51">
+        <f t="shared" si="0"/>
+        <v>2.4210201531685033E-2</v>
+      </c>
+      <c r="O51">
+        <f t="shared" si="0"/>
+        <v>0.40323529411764708</v>
+      </c>
+      <c r="P51">
+        <f t="shared" si="0"/>
+        <v>0.69835294117647062</v>
+      </c>
+      <c r="Q51">
+        <f>G51-P51</f>
+        <v>0.16641176470588215</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17">
+      <c r="B52">
+        <f>AVERAGE(B2:B30)</f>
+        <v>30.310344827586206</v>
+      </c>
+      <c r="C52">
+        <f t="shared" ref="C52:P52" si="1">AVERAGE(C2:C30)</f>
+        <v>53.862068965517238</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="1"/>
+        <v>29.068965517241381</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="1"/>
+        <v>0.55955172413793119</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="1"/>
+        <v>0.97696551724137937</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="1"/>
+        <v>0.68772413793103448</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="1"/>
+        <v>0.1366896551724138</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="1"/>
+        <v>35.344827586206897</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="1"/>
+        <v>0.89655172413793105</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="1"/>
+        <v>45.03448275862069</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="1"/>
+        <v>2.5517241379310347</v>
+      </c>
+      <c r="M52">
+        <f t="shared" si="1"/>
+        <v>2.5026262638056782E-2</v>
+      </c>
+      <c r="N52">
+        <f t="shared" si="1"/>
+        <v>6.0703827091789168E-2</v>
+      </c>
+      <c r="O52">
+        <f t="shared" si="1"/>
+        <v>0.44811034482758622</v>
+      </c>
+      <c r="P52">
+        <f t="shared" si="1"/>
+        <v>0.88289655172413761</v>
+      </c>
+      <c r="Q52">
+        <f>P52-G52</f>
+        <v>0.19517241379310313</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17">
+      <c r="P57" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17">
+      <c r="P58" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17">
+      <c r="P59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17">
+      <c r="P60" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17">
+      <c r="P61" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="P62" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17">
+      <c r="P63" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17">
+      <c r="P64" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="16:16">
+      <c r="P65" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66" spans="16:16">
+      <c r="P66" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="67" spans="16:16">
+      <c r="P67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="16:16">
+      <c r="P68" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" spans="16:16">
+      <c r="P69" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="70" spans="16:16">
+      <c r="P70" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="71" spans="16:16">
+      <c r="P71" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="72" spans="16:16">
+      <c r="P72" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="16:16">
+      <c r="P73" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q50">
+    <sortCondition ref="Q2:Q50"/>
+  </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
